--- a/MEDICIÓN DE TIEMPOS.xlsx
+++ b/MEDICIÓN DE TIEMPOS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bb4d9ba34e02ff95/Escritorio/US/3º/2º CUATRIMESTRE/ASD/TRABAJO-ASD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1758670F-8DDA-4BC9-92AB-28E554A790A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{1758670F-8DDA-4BC9-92AB-28E554A790A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81232FDD-B42E-4535-9248-E5AC58311A81}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{503744F5-AB93-4239-99C6-BD84D2E61CB6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>No optimizado</t>
   </si>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <t>MPI</t>
+  </si>
+  <si>
+    <t>DESENRROLLADO</t>
+  </si>
+  <si>
+    <t>NÚMERO DE HILOS</t>
   </si>
 </sst>
 </file>
@@ -139,23 +145,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -163,11 +155,23 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -201,6 +205,10 @@
     </a>
   </bag>
 </FeaturePropertyBags>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -520,65 +528,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D38E2A-94F1-4840-82B3-7C0072C3C818}">
-  <dimension ref="A2:G13"/>
+  <dimension ref="A2:G15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="1" max="1" width="16.109375" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="5">
+      <c r="B2" s="3">
         <v>46132</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
+      <c r="C2" s="3">
+        <v>46137</v>
+      </c>
+      <c r="D2" s="3">
+        <v>46137</v>
+      </c>
+      <c r="E2" s="3">
+        <v>46137</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="9">
+      <c r="A3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="5">
         <f>(20.426531+21.868803+21.440205)/3</f>
         <v>21.245179666666665</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="C3" s="5">
+        <f>(23.154895+23.233716+22.846403)/3</f>
+        <v>23.078337999999999</v>
+      </c>
+      <c r="D3" s="5">
+        <f>(23.154895+23.233716+22.846403)/3</f>
+        <v>23.078337999999999</v>
+      </c>
+      <c r="E3" s="5">
+        <f>(23.154895+23.233716+22.846403)/3</f>
+        <v>23.078337999999999</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="10"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <f>(2.469501+2.568981+2.42383)/3</f>
         <v>2.4874373333333337</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+      <c r="C5" s="5">
+        <f>(8.100368+8.38925+2.847966)/3</f>
+        <v>6.4458613333333332</v>
+      </c>
+      <c r="D5" s="5">
+        <f>(3.391218+2.48942+3.082873)/3</f>
+        <v>2.9878370000000003</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -587,6 +619,15 @@
       <c r="B8">
         <v>1000</v>
       </c>
+      <c r="C8">
+        <v>1000</v>
+      </c>
+      <c r="D8">
+        <v>1000</v>
+      </c>
+      <c r="E8">
+        <v>1000</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -595,6 +636,15 @@
       <c r="B9">
         <v>1000</v>
       </c>
+      <c r="C9">
+        <v>1000</v>
+      </c>
+      <c r="D9">
+        <v>1000</v>
+      </c>
+      <c r="E9">
+        <v>1000</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -603,6 +653,15 @@
       <c r="B10">
         <v>500</v>
       </c>
+      <c r="C10">
+        <v>500</v>
+      </c>
+      <c r="D10">
+        <v>500</v>
+      </c>
+      <c r="E10">
+        <v>500</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -611,59 +670,118 @@
       <c r="B11">
         <v>500</v>
       </c>
+      <c r="C11">
+        <v>500</v>
+      </c>
+      <c r="D11">
+        <v>500</v>
+      </c>
+      <c r="E11">
+        <v>500</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="C12" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="8" t="b">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" s="8" t="b">
+      <c r="B15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="14">
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B5:B6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
